--- a/plantilla-cotizacion.xlsx
+++ b/plantilla-cotizacion.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -32,6 +32,11 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="11"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="00A9764A"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -64,12 +69,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -438,9 +444,9 @@
   <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="23" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="19" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
     <col width="19" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="17" customWidth="1" min="6" max="6"/>
@@ -479,31 +485,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>María Cecilia Vergara</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>08-09-2026</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Alejandro Vásquez</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>+56 9 4223 4330</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>Pichilemu</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
         <v>30</v>
       </c>
@@ -519,22 +505,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:O6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="14" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="14" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="18" customWidth="1" min="7" max="7"/>
     <col width="21" customWidth="1" min="8" max="8"/>
-    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="21" customWidth="1" min="11" max="11"/>
     <col width="18" customWidth="1" min="12" max="12"/>
-    <col width="40" customWidth="1" min="13" max="13"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -603,100 +589,93 @@
           <t>Notas</t>
         </is>
       </c>
+      <c r="O1" s="2" t="inlineStr">
+        <is>
+          <t>← Estas 4 columnas puedes dejarlas vacías: el cotizador las calcula solo.</t>
+        </is>
+      </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Huingán</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2D-2B</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>1 piso</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>73.8</v>
-      </c>
-      <c r="E2" t="n">
-        <v>37.8</v>
-      </c>
-      <c r="F2" t="n">
-        <v>111.5</v>
-      </c>
-      <c r="G2" t="n">
-        <v>36.5</v>
-      </c>
-      <c r="H2" t="n">
-        <v>6</v>
-      </c>
-      <c r="I2" t="n">
-        <v>2692</v>
-      </c>
-      <c r="J2" t="n">
-        <v>227</v>
-      </c>
-      <c r="K2" t="n">
-        <v>2919</v>
-      </c>
-      <c r="L2" t="n">
-        <v>26.17</v>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Doble altura, amplitud y materiales nobles.</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr"/>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Coihue</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>3D-3B+ESC</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>1 piso</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
-        <v>167.4</v>
-      </c>
-      <c r="E3" t="n">
-        <v>60.5</v>
-      </c>
-      <c r="F3" t="n">
-        <v>227.9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>33</v>
-      </c>
-      <c r="H3" t="n">
-        <v>6</v>
-      </c>
-      <c r="I3" t="n">
-        <v>5524</v>
-      </c>
-      <c r="J3" t="n">
-        <v>363</v>
-      </c>
-      <c r="K3" t="n">
-        <v>5887</v>
-      </c>
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+    </row>
   </sheetData>
+  <dataValidations count="1">
+    <dataValidation sqref="A2:A50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Modelo no reconocido" error="Elige un modelo de la lista o escribe uno nuevo." type="list">
+      <formula1>"Lingue,Huingán,Maitén,Peumo,Roble,Coihue,Otro"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -707,14 +686,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A8"/>
+  <dimension ref="A1:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="110" customWidth="1" min="1" max="1"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="2" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Cómo usar esta planilla</t>
         </is>
@@ -733,35 +712,49 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Hoja 'Datos': una sola fila con los datos del cliente y de la cotización.</t>
+          <t>2. Hoja 'Datos': una sola fila (la fila 2) con los datos del cliente y de la cotización.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>3. Hoja 'Casas': una fila por cada modelo de casa que se está cotizando (puedes agregar todas las que necesites).</t>
+          <t>3. Hoja 'Casas': una fila por cada modelo de casa que se está cotizando. Borra las filas en blanco que no vayas a usar, o agrega más si necesitas cotizar más casas.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>4. Si dejas vacías 'Total UF Útil', 'Total UF Terraza', 'Valor UF Neto + IVA' o 'Valor Prom UF/m2', el cotizador las calcula solo a partir de los m2 y el valor UF/m2.</t>
+          <t>4. La columna 'Modelo' tiene un menú desplegable con los modelos de Neorigen — si el modelo no está en la lista, simplemente escríbelo.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. La columna 'Notas' es opcional — lo que escribas ahí aparece como un recuadro destacado en el PDF de esa casa.</t>
+          <t>5. Puedes dejar vacías 'Total UF Útil', 'Total UF Terraza', 'Valor UF Neto + IVA' y 'Valor Prom UF/m2': el cotizador las calcula solo a partir de los m2 y el valor UF/m2.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>6. Guarda el archivo como .xlsx y súbelo en cotizador.neorigen.cl (o donde se haya publicado la herramienta).</t>
+          <t>6. La columna 'Notas' es opcional — lo que escribas ahí aparece como un recuadro destacado en el PDF de esa casa.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>7. Los números decimales se pueden escribir con coma o con punto (73,8 o 73.8) — ambos funcionan igual.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>8. Guarda el archivo como .xlsx y súbelo en el cotizador (pestaña 'Subir planilla'). El PDF que se genera es siempre de 1 sola página, sin importar cuántas casas hayas cotizado.</t>
         </is>
       </c>
     </row>

--- a/plantilla-cotizacion.xlsx
+++ b/plantilla-cotizacion.xlsx
@@ -441,15 +441,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:I2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="17" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="17" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="19" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -460,27 +463,42 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>Teléfono Cliente</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Correo Cliente</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Fecha</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Vigencia (días)</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Proyecto / Ubicación</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Vendedor</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Teléfono Vendedor</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Proyecto / Ubicación</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Vigencia (días)</t>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Correo Vendedor</t>
         </is>
       </c>
     </row>
@@ -489,10 +507,13 @@
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="n">
+      <c r="E2" t="n">
         <v>30</v>
       </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -673,7 +694,7 @@
   </sheetData>
   <dataValidations count="1">
     <dataValidation sqref="A2:A50" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Modelo no reconocido" error="Elige un modelo de la lista o escribe uno nuevo." type="list">
-      <formula1>"Lingue,Huingán,Maitén,Peumo,Roble,Coihue,Otro"</formula1>
+      <formula1>"Lingue,Huingán,Peumo,Boldo,Huingán Familiar,Roble,Maitén,Coihue,Otro"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -712,7 +733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. Hoja 'Datos': una sola fila (la fila 2) con los datos del cliente y de la cotización.</t>
+          <t>2. Hoja 'Datos': una sola fila (la fila 2) con los datos del cliente, el vendedor y la cotización. Todas las columnas son obligatorias, salvo 'Correo Vendedor' (esa puede quedar vacía).</t>
         </is>
       </c>
     </row>
@@ -754,7 +775,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>8. Guarda el archivo como .xlsx y súbelo en el cotizador (pestaña 'Subir planilla'). El PDF que se genera es siempre de 1 sola página, sin importar cuántas casas hayas cotizado.</t>
+          <t>8. Guarda el archivo como .xlsx y súbelo en el cotizador (pestaña 'Subir planilla'). Si cotizas más de 2-3 casas, el PDF continúa solo en las páginas que hagan falta — siempre respetando el mismo orden y diseño.</t>
         </is>
       </c>
     </row>
